--- a/data.xlsx
+++ b/data.xlsx
@@ -1,40 +1,148 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\bastelsystem3\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06A046A5-3501-45BD-8585-35694AC24662}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="users" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="users" sheetId="1" r:id="rId1"/>
+    <sheet name="TAB" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="30">
+  <si>
+    <t>Full Name</t>
+  </si>
+  <si>
+    <t>Designation</t>
+  </si>
+  <si>
+    <t>Phone Number</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Username</t>
+  </si>
+  <si>
+    <t>Password</t>
+  </si>
+  <si>
+    <t>HETTIARACHCHIGE BHATHIYA PRADEEP KUMARA</t>
+  </si>
+  <si>
+    <t>owner</t>
+  </si>
+  <si>
+    <t>bathiyapradeep@yahoo.com</t>
+  </si>
+  <si>
+    <t>admin1</t>
+  </si>
+  <si>
+    <t>admin</t>
+  </si>
+  <si>
+    <t>HETTIARACHCHIGE HATHIYA PRADEEP KUMARA</t>
+  </si>
+  <si>
+    <t>bathiyapraeeep@yahoo.com</t>
+  </si>
+  <si>
+    <t>admin2</t>
+  </si>
+  <si>
+    <t>bathiya</t>
+  </si>
+  <si>
+    <t>0752480588</t>
+  </si>
+  <si>
+    <t>ba</t>
+  </si>
+  <si>
+    <t>MAIN</t>
+  </si>
+  <si>
+    <t>SUB</t>
+  </si>
+  <si>
+    <t>SUB SUB</t>
+  </si>
+  <si>
+    <t>DASHBOARD</t>
+  </si>
+  <si>
+    <t>JOB</t>
+  </si>
+  <si>
+    <t>SYSTEM</t>
+  </si>
+  <si>
+    <t>AUTOMATION</t>
+  </si>
+  <si>
+    <t>SETTINGS</t>
+  </si>
+  <si>
+    <t>SUMMERY,ALL WORKS,MY WORK,SEARCH</t>
+  </si>
+  <si>
+    <t>NEW SHIPMENT,INVOICE CREATE,CUSDEC,CDN,BARCODE,BOAT NOTE,FINAL DOCS</t>
+  </si>
+  <si>
+    <t>OPEN USER ACCOUNTS,ACCESS,SHIPPER,TEMPLATES,BILLING,WHARF DETAILS,DRIVER DETAILS,</t>
+  </si>
+  <si>
+    <t>BOAT NOTE PASS,EXPORT RELEASE,PAYMENTS</t>
+  </si>
+  <si>
+    <t>PROFILE,SECURITY,SYSYTEM INFO</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -46,93 +154,44 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -420,139 +479,156 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Full Name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Designation</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Phone Number</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Username</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Password</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>HETTIARACHCHIGE BHATHIYA PRADEEP KUMARA</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>owner</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2">
         <v>742532760</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>bathiyapradeep@yahoo.com</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>admin1</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>HETTIARACHCHIGE HATHIYA PRADEEP KUMARA</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>owner</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3">
         <v>742532763</v>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>bathiyapraeeep@yahoo.com</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>admin2</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>bathiya</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>owner</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>0752480588</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>ba</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BB38197-A1E0-4E9E-B8ED-85318BFF09E9}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.28515625" customWidth="1"/>
+    <col min="2" max="2" width="83.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\bastelsystem3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06A046A5-3501-45BD-8585-35694AC24662}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18E96F72-1F38-4C09-AA46-6A07BC978628}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1470" yWindow="735" windowWidth="7755" windowHeight="10185" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="users" sheetId="1" r:id="rId1"/>
@@ -104,13 +104,13 @@
     <t>NEW SHIPMENT,INVOICE CREATE,CUSDEC,CDN,BARCODE,BOAT NOTE,FINAL DOCS</t>
   </si>
   <si>
-    <t>OPEN USER ACCOUNTS,ACCESS,SHIPPER,TEMPLATES,BILLING,WHARF DETAILS,DRIVER DETAILS,</t>
-  </si>
-  <si>
     <t>BOAT NOTE PASS,EXPORT RELEASE,PAYMENTS</t>
   </si>
   <si>
-    <t>PROFILE,SECURITY,SYSYTEM INFO</t>
+    <t>OPEN USER ACCOUNTS,ACCESS,SHIPPER,TEMPLATES,BILLING,WHARF DETAILS,DRIVER DETAILS</t>
+  </si>
+  <si>
+    <t>PROFILE,SECURITY,SYSTEM INFO</t>
   </si>
 </sst>
 </file>
@@ -609,7 +609,7 @@
         <v>22</v>
       </c>
       <c r="B4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -617,7 +617,7 @@
         <v>23</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\bastelsystem3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18E96F72-1F38-4C09-AA46-6A07BC978628}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59FAA735-0C8C-4AE0-8B4B-86090751D048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1470" yWindow="735" windowWidth="7755" windowHeight="10185" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="users" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="34">
   <si>
     <t>Full Name</t>
   </si>
@@ -41,7 +41,13 @@
     <t>Password</t>
   </si>
   <si>
-    <t>HETTIARACHCHIGE BHATHIYA PRADEEP KUMARA</t>
+    <t>Main</t>
+  </si>
+  <si>
+    <t>Sub</t>
+  </si>
+  <si>
+    <t>Rashmitha</t>
   </si>
   <si>
     <t>owner</t>
@@ -50,30 +56,36 @@
     <t>bathiyapradeep@yahoo.com</t>
   </si>
   <si>
-    <t>admin1</t>
-  </si>
-  <si>
-    <t>admin</t>
-  </si>
-  <si>
-    <t>HETTIARACHCHIGE HATHIYA PRADEEP KUMARA</t>
+    <t>Tharaka</t>
   </si>
   <si>
     <t>bathiyapraeeep@yahoo.com</t>
   </si>
   <si>
-    <t>admin2</t>
+    <t>AUTOMATION, DASHBOARD</t>
+  </si>
+  <si>
+    <t>EXPORT RELEASE, PAYMENTS</t>
   </si>
   <si>
     <t>bathiya</t>
   </si>
   <si>
-    <t>0752480588</t>
-  </si>
-  <si>
     <t>ba</t>
   </si>
   <si>
+    <t>worker</t>
+  </si>
+  <si>
+    <t>rashmitha1</t>
+  </si>
+  <si>
+    <t>tharaka1</t>
+  </si>
+  <si>
+    <t>bathiya1</t>
+  </si>
+  <si>
     <t>MAIN</t>
   </si>
   <si>
@@ -86,28 +98,28 @@
     <t>DASHBOARD</t>
   </si>
   <si>
+    <t>SUMMERY,ALL WORKS,MY WORK,SEARCH</t>
+  </si>
+  <si>
     <t>JOB</t>
   </si>
   <si>
+    <t>NEW SHIPMENT,INVOICE CREATE,CUSDEC,CDN,BARCODE,BOAT NOTE,FINAL DOCS</t>
+  </si>
+  <si>
     <t>SYSTEM</t>
   </si>
   <si>
+    <t>OPEN USER ACCOUNTS,ACCESS,SHIPPER,TEMPLATES,BILLING,WHARF DETAILS,DRIVER DETAILS</t>
+  </si>
+  <si>
     <t>AUTOMATION</t>
   </si>
   <si>
+    <t>BOAT NOTE PASS,EXPORT RELEASE,PAYMENTS</t>
+  </si>
+  <si>
     <t>SETTINGS</t>
-  </si>
-  <si>
-    <t>SUMMERY,ALL WORKS,MY WORK,SEARCH</t>
-  </si>
-  <si>
-    <t>NEW SHIPMENT,INVOICE CREATE,CUSDEC,CDN,BARCODE,BOAT NOTE,FINAL DOCS</t>
-  </si>
-  <si>
-    <t>BOAT NOTE PASS,EXPORT RELEASE,PAYMENTS</t>
-  </si>
-  <si>
-    <t>OPEN USER ACCOUNTS,ACCESS,SHIPPER,TEMPLATES,BILLING,WHARF DETAILS,DRIVER DETAILS</t>
   </si>
   <si>
     <t>PROFILE,SECURITY,SYSTEM INFO</t>
@@ -172,11 +184,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -480,10 +493,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -502,33 +515,39 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C2">
         <v>742532760</v>
       </c>
       <c r="D2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C3">
         <v>742532763</v>
@@ -537,30 +556,36 @@
         <v>12</v>
       </c>
       <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s">
         <v>13</v>
       </c>
-      <c r="F3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" t="s">
-        <v>15</v>
+        <v>9</v>
+      </c>
+      <c r="C4">
+        <v>752480588</v>
       </c>
       <c r="D4" t="s">
         <v>16</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -569,64 +594,65 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BB38197-A1E0-4E9E-B8ED-85318BFF09E9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8D07AFC-E921-4BEE-B0DD-5F3F6EE83D4C}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="15.28515625" customWidth="1"/>
-    <col min="2" max="2" width="83.140625" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>19</v>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>25</v>
       </c>
+      <c r="C2" s="2"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="A3" s="2" t="s">
         <v>26</v>
       </c>
+      <c r="B3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="2"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="A4" s="2" t="s">
         <v>28</v>
       </c>
+      <c r="B4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="2"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5" t="s">
-        <v>27</v>
-      </c>
+      <c r="A5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="2"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" t="s">
-        <v>29</v>
-      </c>
+      <c r="A6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\bastelsystem3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59FAA735-0C8C-4AE0-8B4B-86090751D048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82E4D8B6-AD4F-456D-95C1-86A6654BE676}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="36">
   <si>
     <t>Full Name</t>
   </si>
@@ -50,40 +50,46 @@
     <t>Rashmitha</t>
   </si>
   <si>
+    <t>worker</t>
+  </si>
+  <si>
+    <t>bathiyapradeep@yahoo.com</t>
+  </si>
+  <si>
+    <t>rashmitha1</t>
+  </si>
+  <si>
+    <t>AUTOMATION, DASHBOARD</t>
+  </si>
+  <si>
+    <t>BOAT NOTE PASS, EXPORT RELEASE, PAYMENTS</t>
+  </si>
+  <si>
+    <t>Tharaka</t>
+  </si>
+  <si>
+    <t>bathiyapraeeep@yahoo.com</t>
+  </si>
+  <si>
+    <t>tharaka1</t>
+  </si>
+  <si>
+    <t>EXPORT RELEASE, PAYMENTS</t>
+  </si>
+  <si>
+    <t>bathiya</t>
+  </si>
+  <si>
     <t>owner</t>
   </si>
   <si>
-    <t>bathiyapradeep@yahoo.com</t>
-  </si>
-  <si>
-    <t>Tharaka</t>
-  </si>
-  <si>
-    <t>bathiyapraeeep@yahoo.com</t>
-  </si>
-  <si>
-    <t>AUTOMATION, DASHBOARD</t>
-  </si>
-  <si>
-    <t>EXPORT RELEASE, PAYMENTS</t>
-  </si>
-  <si>
-    <t>bathiya</t>
-  </si>
-  <si>
     <t>ba</t>
   </si>
   <si>
-    <t>worker</t>
-  </si>
-  <si>
-    <t>rashmitha1</t>
-  </si>
-  <si>
-    <t>tharaka1</t>
-  </si>
-  <si>
     <t>bathiya1</t>
+  </si>
+  <si>
+    <t>admin</t>
   </si>
   <si>
     <t>MAIN</t>
@@ -184,12 +190,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -493,7 +498,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -527,7 +532,7 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C2">
         <v>742532760</v>
@@ -536,56 +541,82 @@
         <v>10</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>18</v>
+        <v>11</v>
+      </c>
+      <c r="G2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C3">
         <v>742532763</v>
       </c>
       <c r="D3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" t="s">
         <v>12</v>
       </c>
-      <c r="E3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" t="s">
-        <v>13</v>
-      </c>
       <c r="H3" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C4">
         <v>752480588</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E4" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F4" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -594,65 +625,64 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8D07AFC-E921-4BEE-B0DD-5F3F6EE83D4C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C573B8C7-52C9-4398-8641-6ABB576F9D65}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.28515625" customWidth="1"/>
+    <col min="2" max="2" width="83.140625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C1" s="3" t="s">
+    <row r="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>23</v>
       </c>
+      <c r="B1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C2" s="2"/>
+      <c r="A2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3" s="2"/>
+      <c r="A3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4" s="2"/>
+      <c r="A4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C5" s="2"/>
+      <c r="A5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C6" s="2"/>
+      <c r="A6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" t="s">
+        <v>35</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -1,157 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\bastelsystem3\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82E4D8B6-AD4F-456D-95C1-86A6654BE676}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="users" sheetId="1" r:id="rId1"/>
-    <sheet name="TAB" sheetId="2" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="users" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="messages" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TAB" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="36">
-  <si>
-    <t>Full Name</t>
-  </si>
-  <si>
-    <t>Designation</t>
-  </si>
-  <si>
-    <t>Phone Number</t>
-  </si>
-  <si>
-    <t>Email</t>
-  </si>
-  <si>
-    <t>Username</t>
-  </si>
-  <si>
-    <t>Password</t>
-  </si>
-  <si>
-    <t>Main</t>
-  </si>
-  <si>
-    <t>Sub</t>
-  </si>
-  <si>
-    <t>Rashmitha</t>
-  </si>
-  <si>
-    <t>worker</t>
-  </si>
-  <si>
-    <t>bathiyapradeep@yahoo.com</t>
-  </si>
-  <si>
-    <t>rashmitha1</t>
-  </si>
-  <si>
-    <t>AUTOMATION, DASHBOARD</t>
-  </si>
-  <si>
-    <t>BOAT NOTE PASS, EXPORT RELEASE, PAYMENTS</t>
-  </si>
-  <si>
-    <t>Tharaka</t>
-  </si>
-  <si>
-    <t>bathiyapraeeep@yahoo.com</t>
-  </si>
-  <si>
-    <t>tharaka1</t>
-  </si>
-  <si>
-    <t>EXPORT RELEASE, PAYMENTS</t>
-  </si>
-  <si>
-    <t>bathiya</t>
-  </si>
-  <si>
-    <t>owner</t>
-  </si>
-  <si>
-    <t>ba</t>
-  </si>
-  <si>
-    <t>bathiya1</t>
-  </si>
-  <si>
-    <t>admin</t>
-  </si>
-  <si>
-    <t>MAIN</t>
-  </si>
-  <si>
-    <t>SUB</t>
-  </si>
-  <si>
-    <t>SUB SUB</t>
-  </si>
-  <si>
-    <t>DASHBOARD</t>
-  </si>
-  <si>
-    <t>SUMMERY,ALL WORKS,MY WORK,SEARCH</t>
-  </si>
-  <si>
-    <t>JOB</t>
-  </si>
-  <si>
-    <t>NEW SHIPMENT,INVOICE CREATE,CUSDEC,CDN,BARCODE,BOAT NOTE,FINAL DOCS</t>
-  </si>
-  <si>
-    <t>SYSTEM</t>
-  </si>
-  <si>
-    <t>OPEN USER ACCOUNTS,ACCESS,SHIPPER,TEMPLATES,BILLING,WHARF DETAILS,DRIVER DETAILS</t>
-  </si>
-  <si>
-    <t>AUTOMATION</t>
-  </si>
-  <si>
-    <t>BOAT NOTE PASS,EXPORT RELEASE,PAYMENTS</t>
-  </si>
-  <si>
-    <t>SETTINGS</t>
-  </si>
-  <si>
-    <t>PROFILE,SECURITY,SYSTEM INFO</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="Calibri"/>
+      <b val="1"/>
       <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -191,25 +74,84 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -497,126 +439,228 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Full Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Designation</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Phone Number</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Username</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Password</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Sub</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Rashmitha</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>worker</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
         <v>742532760</v>
       </c>
-      <c r="D2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3">
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>bathiyapradeep@yahoo.com</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>rashmitha1</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>rashmitha1</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>AUTOMATION, DASHBOARD</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>BOAT NOTE PASS, EXPORT RELEASE, PAYMENTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Tharaka</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>worker</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
         <v>742532763</v>
       </c>
-      <c r="D3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4">
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>bathiyapraeeep@yahoo.com</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>tharaka1</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>tharaka1</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>AUTOMATION, DASHBOARD</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>EXPORT RELEASE, PAYMENTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>bathiya</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>owner</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
         <v>752480588</v>
       </c>
-      <c r="D4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5" t="s">
-        <v>22</v>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ba</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>bathiya1</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>bathiya1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>stela</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>accountant</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0752788404</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>stelamanori@gmail.com</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>stela</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>stela1</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -625,63 +669,195 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C573B8C7-52C9-4398-8641-6ABB576F9D65}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>from_user</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>to_user</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>message</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>is_read</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>tharaka1</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ADO KOHOMADHA</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-04-30 12:37:22</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>tharaka1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>hodai ban</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-04-30 12:41:30</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="15.28515625" customWidth="1"/>
-    <col min="2" max="2" width="83.140625" customWidth="1"/>
+    <col width="15.28515625" customWidth="1" min="1" max="1"/>
+    <col width="83.140625" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" t="s">
-        <v>35</v>
+    <row r="1" customFormat="1" s="2">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>MAIN</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>SUB</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>SUB SUB</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>DASHBOARD</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SUMMERY,ALL WORKS,MY WORK,SEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>JOB</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>NEW SHIPMENT,INVOICE CREATE,CUSDEC,CDN,BARCODE,BOAT NOTE,FINAL DOCS</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SYSTEM</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>OPEN USER ACCOUNTS,ACCESS,SHIPPER,TEMPLATES,BILLING,WHARF DETAILS,DRIVER DETAILS</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AUTOMATION</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BOAT NOTE PASS,EXPORT RELEASE,PAYMENTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SETTINGS</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>PROFILE,SECURITY,SYSTEM INFO</t>
+        </is>
       </c>
     </row>
   </sheetData>
